--- a/output/lettera13.xlsx
+++ b/output/lettera13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="66">
   <si>
     <t>word</t>
   </si>
@@ -25,7 +25,7 @@
     <t>lemma</t>
   </si>
   <si>
-    <t>Molto</t>
+    <t>r</t>
   </si>
   <si>
     <t>Illustre</t>
@@ -34,271 +34,184 @@
     <t>Signor</t>
   </si>
   <si>
-    <t>cuggino</t>
+    <t>Mi</t>
+  </si>
+  <si>
+    <t>sono</t>
+  </si>
+  <si>
+    <t>stati</t>
+  </si>
+  <si>
+    <t>gratissimi</t>
+  </si>
+  <si>
+    <t>li</t>
+  </si>
+  <si>
+    <t>avisi</t>
+  </si>
+  <si>
+    <t>che</t>
+  </si>
+  <si>
+    <t>Vostra</t>
+  </si>
+  <si>
+    <t>Signoria</t>
+  </si>
+  <si>
+    <t>m’ha</t>
+  </si>
+  <si>
+    <t>dati</t>
+  </si>
+  <si>
+    <t>per</t>
+  </si>
+  <si>
+    <t>le</t>
+  </si>
+  <si>
+    <t>sue</t>
+  </si>
+  <si>
+    <t>delli</t>
   </si>
   <si>
     <t>e</t>
   </si>
   <si>
-    <t>fratello</t>
-  </si>
-  <si>
-    <t>honorando</t>
-  </si>
-  <si>
-    <t>Il</t>
-  </si>
-  <si>
-    <t>Palladio</t>
-  </si>
-  <si>
-    <t>non</t>
-  </si>
-  <si>
-    <t>è</t>
-  </si>
-  <si>
-    <t>possuto</t>
-  </si>
-  <si>
-    <t>venire</t>
-  </si>
-  <si>
-    <t>in</t>
-  </si>
-  <si>
-    <t>là</t>
-  </si>
-  <si>
-    <t>con</t>
-  </si>
-  <si>
-    <t>questo</t>
-  </si>
-  <si>
-    <t>corriere</t>
-  </si>
-  <si>
-    <t>perché</t>
-  </si>
-  <si>
-    <t>gl’è</t>
-  </si>
-  <si>
-    <t>convenuto</t>
-  </si>
-  <si>
-    <t>andare</t>
-  </si>
-  <si>
-    <t>fuori</t>
+    <t>del</t>
+  </si>
+  <si>
+    <t>passato</t>
+  </si>
+  <si>
+    <t>ne</t>
+  </si>
+  <si>
+    <t>la</t>
+  </si>
+  <si>
+    <t>ringratio</t>
+  </si>
+  <si>
+    <t>molto</t>
+  </si>
+  <si>
+    <t>sì</t>
+  </si>
+  <si>
+    <t>come</t>
+  </si>
+  <si>
+    <t>faccio</t>
+  </si>
+  <si>
+    <t>anchora</t>
   </si>
   <si>
     <t>della</t>
   </si>
   <si>
-    <t>terra</t>
-  </si>
-  <si>
-    <t>per</t>
-  </si>
-  <si>
-    <t>certi</t>
-  </si>
-  <si>
-    <t>suoi</t>
-  </si>
-  <si>
-    <t>servitii</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>risoluto</t>
-  </si>
-  <si>
-    <t>nondimeno</t>
-  </si>
-  <si>
-    <t>di</t>
-  </si>
-  <si>
-    <t>volere</t>
-  </si>
-  <si>
-    <t>venirvi</t>
-  </si>
-  <si>
-    <t>questa</t>
-  </si>
-  <si>
-    <t>setti</t>
-  </si>
-  <si>
-    <t>mana</t>
-  </si>
-  <si>
-    <t>mostra</t>
-  </si>
-  <si>
-    <t>desiderio</t>
-  </si>
-  <si>
-    <t>grande</t>
-  </si>
-  <si>
-    <t>compiacerla</t>
-  </si>
-  <si>
-    <t>quel</t>
-  </si>
-  <si>
-    <t>che</t>
+    <t>amorevolezza</t>
+  </si>
+  <si>
+    <t>solita</t>
+  </si>
+  <si>
+    <t>sudette</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
+    <t>ha</t>
+  </si>
+  <si>
+    <t>mostrata</t>
+  </si>
+  <si>
+    <t>VER:impe</t>
+  </si>
+  <si>
+    <t>ADJ</t>
+  </si>
+  <si>
+    <t>NOM</t>
+  </si>
+  <si>
+    <t>PRO:pers</t>
+  </si>
+  <si>
+    <t>VER:pres</t>
+  </si>
+  <si>
+    <t>VER:pper</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>PRO:poss</t>
+  </si>
+  <si>
+    <t>PRE</t>
+  </si>
+  <si>
+    <t>DET:def</t>
+  </si>
+  <si>
+    <t>PRE:det</t>
+  </si>
+  <si>
+    <t>ADV</t>
+  </si>
+  <si>
+    <t>PRO:rela</t>
+  </si>
+  <si>
+    <t>illustre</t>
+  </si>
+  <si>
+    <t>signore</t>
+  </si>
+  <si>
+    <t>essere</t>
+  </si>
+  <si>
+    <t>essere|stare</t>
+  </si>
+  <si>
+    <t>grato</t>
+  </si>
+  <si>
+    <t>vostro</t>
+  </si>
+  <si>
+    <t>signoria</t>
+  </si>
+  <si>
+    <t>dato</t>
   </si>
   <si>
     <t>il</t>
   </si>
   <si>
-    <t>può</t>
-  </si>
-  <si>
-    <t>hauto</t>
-  </si>
-  <si>
-    <t>carissimo</t>
-  </si>
-  <si>
-    <t>intendere</t>
-  </si>
-  <si>
-    <t>le</t>
-  </si>
-  <si>
-    <t>restino</t>
-  </si>
-  <si>
-    <t>sattisfatte</t>
-  </si>
-  <si>
-    <t>lui</t>
-  </si>
-  <si>
-    <t>qui</t>
-  </si>
-  <si>
-    <t>faccendo</t>
-  </si>
-  <si>
-    <t>fine</t>
-  </si>
-  <si>
-    <t>li</t>
-  </si>
-  <si>
-    <t>bascio</t>
-  </si>
-  <si>
-    <t>la</t>
-  </si>
-  <si>
-    <t>mano</t>
-  </si>
-  <si>
-    <t>ADV</t>
-  </si>
-  <si>
-    <t>ADJ</t>
-  </si>
-  <si>
-    <t>NOM</t>
-  </si>
-  <si>
-    <t>CON</t>
-  </si>
-  <si>
-    <t>VER:geru</t>
-  </si>
-  <si>
-    <t>DET:def</t>
-  </si>
-  <si>
-    <t>VER:pres</t>
-  </si>
-  <si>
-    <t>VER:infi</t>
-  </si>
-  <si>
-    <t>PRE</t>
-  </si>
-  <si>
-    <t>PRO:demo</t>
-  </si>
-  <si>
-    <t>VER:pper</t>
-  </si>
-  <si>
-    <t>PRE:det</t>
-  </si>
-  <si>
-    <t>PRO:poss</t>
-  </si>
-  <si>
-    <t>PRO:pers</t>
-  </si>
-  <si>
-    <t>PRO:rela</t>
-  </si>
-  <si>
-    <t>VER:cpre</t>
-  </si>
-  <si>
-    <t>molto</t>
-  </si>
-  <si>
-    <t>illustre</t>
-  </si>
-  <si>
-    <t>signore</t>
-  </si>
-  <si>
-    <t>palladio</t>
-  </si>
-  <si>
-    <t>essere</t>
-  </si>
-  <si>
-    <t>convenire</t>
-  </si>
-  <si>
-    <t>del</t>
-  </si>
-  <si>
-    <t>certo</t>
-  </si>
-  <si>
     <t>suo</t>
   </si>
   <si>
-    <t>si</t>
-  </si>
-  <si>
-    <t>setto</t>
-  </si>
-  <si>
-    <t>compiacere</t>
-  </si>
-  <si>
-    <t>quello</t>
-  </si>
-  <si>
-    <t>potere</t>
-  </si>
-  <si>
-    <t>caro</t>
-  </si>
-  <si>
-    <t>restare</t>
+    <t>fare</t>
+  </si>
+  <si>
+    <t>solito</t>
+  </si>
+  <si>
+    <t>avere</t>
+  </si>
+  <si>
+    <t>mostrare</t>
   </si>
 </sst>
 </file>
@@ -656,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -675,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -686,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -697,10 +610,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -708,10 +621,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -719,10 +632,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -730,10 +643,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -741,10 +654,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -752,10 +665,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -763,10 +676,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -774,7 +687,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -785,10 +698,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -796,10 +709,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -807,7 +720,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -818,10 +731,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -829,7 +742,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
@@ -840,10 +753,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -851,10 +764,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -862,7 +775,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
@@ -873,7 +786,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
@@ -884,7 +797,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -895,120 +808,120 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1016,7 +929,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
         <v>33</v>
@@ -1027,43 +940,43 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" t="s">
         <v>63</v>
-      </c>
-      <c r="C34" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1071,7 +984,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
         <v>35</v>
@@ -1079,343 +992,35 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>21</v>
-      </c>
-      <c r="B42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" t="s">
         <v>65</v>
-      </c>
-      <c r="C43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" t="s">
-        <v>68</v>
-      </c>
-      <c r="C51" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C54" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56" t="s">
-        <v>77</v>
-      </c>
-      <c r="C56" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58" t="s">
-        <v>78</v>
-      </c>
-      <c r="C58" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" t="s">
-        <v>73</v>
-      </c>
-      <c r="C59" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>35</v>
-      </c>
-      <c r="B60" t="s">
-        <v>71</v>
-      </c>
-      <c r="C60" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" t="s">
-        <v>66</v>
-      </c>
-      <c r="C62" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64" t="s">
-        <v>67</v>
-      </c>
-      <c r="C64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" t="s">
-        <v>65</v>
-      </c>
-      <c r="C65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>59</v>
-      </c>
-      <c r="B66" t="s">
-        <v>76</v>
-      </c>
-      <c r="C66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67" t="s">
-        <v>69</v>
-      </c>
-      <c r="C67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69" t="s">
-        <v>65</v>
-      </c>
-      <c r="C69" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
